--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
+          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1692)</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Technology</t>
+          <t>Senior Data Engineer (P1692)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
+          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
+          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pero Family Farms</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Delray Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
+          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Almont, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Almont, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grid Elevated</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618a1dbe7d6ef58d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud-Native Applications</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, DynamoDB, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61eba61db8d1d33f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63633a8200979a09</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Grid Elevated</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=618a1dbe7d6ef58d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer, Clinical Operations</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
+          <t>https://www.indeed.com/viewjob?jk=63633a8200979a09</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Synapse Health</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Skokie, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a6c99045779145</t>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>JPS Tech Solutions pvt ltd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer, Clinical Operations</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Synapse Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Skokie, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
+          <t>https://www.indeed.com/viewjob?jk=38a6c99045779145</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Healthcare Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Nephrocare Dialysis, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Functional Netsuite Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Technical Product Owner - Snowflake</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>FHLBank San Francisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Solutions Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Charter Schools USA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Qarbon Aerospace</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Red Oak, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
+          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,15 +2586,225 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Santa Barbara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CareScout</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Flexjet, LLC.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
         </is>

--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
+          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
+          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pero Family Farms</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Delray Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pero Family Farms</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Delray Beach, FL, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
+          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Almont, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Almont, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
+          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Data Engineer II - OIT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grid Elevated</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618a1dbe7d6ef58d</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63633a8200979a09</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>JPS Tech Solutions pvt ltd</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Data Engineer, Clinical Operations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Synapse Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Skokie, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
+          <t>https://www.indeed.com/viewjob?jk=38a6c99045779145</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer, Clinical Operations</t>
+          <t>Healthcare Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Nephrocare Dialysis, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Functional Netsuite Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Synapse Health</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Skokie, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a6c99045779145</t>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
         </is>
       </c>
     </row>
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
+          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
+          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Technical Product Owner - Snowflake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FHLBank San Francisco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Cloud Solutions Associate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>Charter Schools USA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>IT Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>Qarbon Aerospace</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Red Oak, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>Acceldata</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>Software Engineer - Backend Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,85 +2726,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Flexjet, LLC.</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
         </is>

--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pero Family Farms</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Delray Beach, FL, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>Pero Family Farms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Delray Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Almont, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
+          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Almont, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Data Engineer II - OIT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II - OIT</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>JPS Tech Solutions pvt ltd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Data Engineer, Clinical Operations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer, Clinical Operations</t>
+          <t>Healthcare Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Nephrocare Dialysis, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Functional Netsuite Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Synapse Health</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Skokie, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a6c99045779145</t>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
         </is>
       </c>
     </row>
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
+          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Product Owner - Snowflake</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FHLBank San Francisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Cloud Solutions Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Charter Schools USA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>IT Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>Qarbon Aerospace</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Red Oak, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acceldata</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Developer</t>
+          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Acceldata</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer - Backend Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,182 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Software Engineer Sr</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Farmers Branch, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Fidelity TalentSource</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Westlake, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>CareScout</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Flexjet, LLC.</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Senior Software Data Architect (Phoenix)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
+          <t>https://www.indeed.com/viewjob?jk=748c7729e8f9ad32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1692)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
+          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Technology</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer (P1692)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
         </is>
       </c>
     </row>
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Almont, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,54 +1196,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer II - OIT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II - OIT</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Data Engineer, Clinical Operations</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Healthcare Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>Nephrocare Dialysis, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer, Clinical Operations</t>
+          <t>Functional Netsuite Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
         </is>
       </c>
     </row>
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>Co-Op Data Science/Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>CSL Plasma</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=04d905bcd26c07f0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
+          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
+          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Product Owner - Snowflake</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Data Integration Engineer / ETL Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Concept Plus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
+          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>FHLBank San Francisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>Cloud Solutions Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>Charter Schools USA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>IT Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>Qarbon Aerospace</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Red Oak, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Architect - Pharma domain- W2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Acceldata</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Washington, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>Software Engineer - Backend Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
+          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acceldata</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, VA, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Developer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,87 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>CareScout</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb05c2c61999715</t>
+          <t>https://www.indeed.com/viewjob?jk=14e0af7fcb6718f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect (Phoenix)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7eb8898b893b80</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bbc064985e6d03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748c7729e8f9ad32</t>
+          <t>https://www.indeed.com/viewjob?jk=2f059896b1dc8546</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Agentic AI Engineer (AWS &amp; Azure)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc8098824f5428a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Software Data Architect (Phoenix)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1692)</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
+          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,85 +828,85 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22caac5643ade2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=748c7729e8f9ad32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=f1770e68ca0a7f94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pero Family Farms</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delray Beach, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>Data Engineer IV (6226)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=966a231d0ac3ac5d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
+          <t>Senior Full Stack Developer - New York</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5159354fa31a01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
+          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>Pero Family Farms</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Delray Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8965662ac1318ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1f6d405ab4fefc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II - OIT</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
+          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, Dask, Data Modeling, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
+          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Clinical Operations</t>
+          <t>Data Engineer II - OIT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,42 +1441,42 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>BusPatrol</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=68a96aefdc270e6c</t>
         </is>
       </c>
     </row>
@@ -1488,20 +1488,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6f578efcb4c089b6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer, Clinical Operations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Co-Op Data Science/Analytics</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CSL Plasma</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d905bcd26c07f0</t>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Healthcare Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Nephrocare Dialysis, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, pytest</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55cc546d0261279c</t>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
+          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
+          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>Forman Technology Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, SQL Server, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f86de95c2e4071</t>
         </is>
       </c>
     </row>
@@ -2008,60 +2008,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Integration Engineer / ETL Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concept Plus</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
+          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Technical Product Owner - Snowflake</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>Data Integration Engineer / ETL Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>Concept Plus</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FHLBank San Francisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Cloud Solutions Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>Charter Schools USA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Power BI Architect - Pharma domain- W2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>Power BI Architect - Pharma domain- W2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
+          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Acceldata</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, Cassandra, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - Backend Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
+          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Developer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Acceldata</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,52 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer BI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>Quality Bicycle Products GBC / QBP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e0af7fcb6718f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcb545e0d7339df</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7eb8898b893b80</t>
+          <t>https://www.indeed.com/viewjob?jk=14e0af7fcb6718f5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, API Gateway, ECS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bbc064985e6d03</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7eb8898b893b80</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f059896b1dc8546</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bbc064985e6d03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer (AWS &amp; Azure)</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Azure, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc8098824f5428a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f059896b1dc8546</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect (Phoenix)</t>
+          <t>Agentic AI Engineer (AWS &amp; Azure)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc8098824f5428a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Senior Software Data Architect (Phoenix)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - New York</t>
+          <t>DevOps Engineer II - Data and Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,207 +1021,207 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5159354fa31a01</t>
+          <t>https://www.indeed.com/viewjob?jk=53108c9bd68716fa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>DevOps Engineer II - Data and Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=f2217093bc52c879</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>Senior Full Stack Developer - New York</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5159354fa31a01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pero Family Farms</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Delray Beach, FL, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Azure, Google Cloud Platform, GCP, Hive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
+          <t>https://www.indeed.com/viewjob?jk=7744c06eb8bcb1d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73a795e20ebb26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
+          <t>https://www.indeed.com/viewjob?jk=f293050f94f852b1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,172 +1231,172 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1f6d405ab4fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=b685af16a4e1a32c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
+          <t>https://www.indeed.com/viewjob?jk=401ff47825aadd13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb43d49de8a46b2a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fb77a8047e2cb8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=72319d23cc87f97d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, Dask, Data Modeling, DataOps, MLOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=bad85604b0a1225d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II - OIT</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
+          <t>https://www.indeed.com/viewjob?jk=af5d8aeb243630fb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BusPatrol</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,137 +1476,137 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a96aefdc270e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fad39d3239661981</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=6cbd10dae618111f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=6409177a32a82f42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f578efcb4c089b6</t>
+          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Pero Family Farms</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Delray Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
+          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer, Clinical Operations</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Engineer, DevOps - Austin</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CS Disco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, ECS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4fabdb31d720bc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>AI Developer and Fintech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=94608c3ac7b4dac5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, Dask, Data Modeling, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer II - OIT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Forman Technology Group</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>BusPatrol</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, SQL Server, Power BI, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f86de95c2e4071</t>
+          <t>https://www.indeed.com/viewjob?jk=68a96aefdc270e6c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=6f578efcb4c089b6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Integration Engineer / ETL Developer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concept Plus</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,77 +2106,77 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
+          <t>https://www.indeed.com/viewjob?jk=859a8b68a930992d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d34fc4ec0585703</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccc4b2641f8512d</t>
         </is>
       </c>
     </row>
@@ -2188,125 +2188,125 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=850828fdab44abc4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Power BI Architect - Pharma domain- W2</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer Sr</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Forman Technology Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a633ddedf196b66</t>
+          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, Cassandra, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, SQL Server, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f86de95c2e4071</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Technical Product Owner - Snowflake</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=59d7a15394ef2be5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Integration Engineer / ETL Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Concept Plus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acceldata</t>
+          <t>FHLBank San Francisco</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Power BI Architect - Pharma domain- W2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,15 +2516,260 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, Cassandra, Splunk</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend Developer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7-Eleven</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Santa Barbara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Washington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
         </is>

--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HAVI Logistics GmbH</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7eb8898b893b80</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bbc064985e6d03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, API Gateway, ECS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bbc064985e6d03</t>
+          <t>https://www.indeed.com/viewjob?jk=2f059896b1dc8546</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Agentic AI Engineer (AWS &amp; Azure)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f059896b1dc8546</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc8098824f5428a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer (AWS &amp; Azure)</t>
+          <t>Senior Software Data Architect (Phoenix)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Azure, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc8098824f5428a</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect (Phoenix)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f3ddd34aabe8</t>
+          <t>https://www.indeed.com/viewjob?jk=748c7729e8f9ad32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748c7729e8f9ad32</t>
+          <t>https://www.indeed.com/viewjob?jk=f1770e68ca0a7f94</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1770e68ca0a7f94</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98bbbcdc847f11c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7891b7fbaff3f7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8f9f1d8dd81324</t>
+          <t>https://www.indeed.com/viewjob?jk=4a787addd6be5560</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - New York</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Azure, Google Cloud Platform, GCP, Hive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5159354fa31a01</t>
+          <t>https://www.indeed.com/viewjob?jk=7744c06eb8bcb1d6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Azure, Google Cloud Platform, GCP, Hive</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7744c06eb8bcb1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73a795e20ebb26</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73a795e20ebb26</t>
+          <t>https://www.indeed.com/viewjob?jk=f293050f94f852b1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f293050f94f852b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b685af16a4e1a32c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b685af16a4e1a32c</t>
+          <t>https://www.indeed.com/viewjob?jk=401ff47825aadd13</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401ff47825aadd13</t>
+          <t>https://www.indeed.com/viewjob?jk=cb43d49de8a46b2a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb43d49de8a46b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fb77a8047e2cb8</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fb77a8047e2cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=72319d23cc87f97d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72319d23cc87f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=bad85604b0a1225d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad85604b0a1225d</t>
+          <t>https://www.indeed.com/viewjob?jk=af5d8aeb243630fb</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5d8aeb243630fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fad39d3239661981</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad39d3239661981</t>
+          <t>https://www.indeed.com/viewjob?jk=6cbd10dae618111f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Full Stack Developer - New York</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cbd10dae618111f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5159354fa31a01</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Research Application Support Engineer - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=60c86e0a3c8c7263</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pero Family Farms</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Delray Beach, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c027e67f35f12298</t>
+          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=8257cbceb473c52a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer, DevOps - Austin</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CS Disco</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, ECS, Scala, DynamoDB</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4fabdb31d720bc</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Developer and Fintech</t>
+          <t>Engineer, DevOps - Austin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CS Disco</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, ECS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,94 +1721,94 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94608c3ac7b4dac5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4fabdb31d720bc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sorenson Communications</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41305de4a58ac</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Systems Analyst - Semantic Layer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, NoSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3ffb67df20da06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>GIS Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,112 +1816,112 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8c2320056095b2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AI Developer and Fintech</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=94608c3ac7b4dac5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, Dask, Data Modeling, DataOps, MLOps</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II - OIT</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BusPatrol</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a96aefdc270e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3650e6daa027c0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, Dask, Data Modeling, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f578efcb4c089b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II - OIT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>BusPatrol</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859a8b68a930992d</t>
+          <t>https://www.indeed.com/viewjob?jk=68a96aefdc270e6c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d34fc4ec0585703</t>
+          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccc4b2641f8512d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f578efcb4c089b6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850828fdab44abc4</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5e6092f64fb827</t>
+          <t>https://www.indeed.com/viewjob?jk=859a8b68a930992d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Forman Technology Group</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Git</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d34fc4ec0585703</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, SQL Server, Power BI, Azure DevOps, Git</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f86de95c2e4071</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccc4b2641f8512d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CONFIDO</t>
+          <t>Virtusa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf6fb4571a3c426</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>Data Engineer – Advanced Analytics &amp; Fraud Detection</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>TLN Worldwide Enterprises Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=97e726717dc24fb3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d7a15394ef2be5</t>
+          <t>https://www.indeed.com/viewjob?jk=18521f120cecfb99</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Integration Engineer / ETL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Concept Plus</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
+          <t>https://www.indeed.com/viewjob?jk=850828fdab44abc4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Sr. Software Engineer-Java, Spring Boot (Onsite)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7f4539113a6169</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Power BI Architect - Pharma domain- W2</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cbdf8c3d5d2aa6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
+          <t>Data Scientist – Demand Forecasting</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, Cassandra, Splunk</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, ELT, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=fbd0bba4b9b97da0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>IMA Financial Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
+          <t>https://www.indeed.com/viewjob?jk=64c474cf1adc8532</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, SQL Server, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f86de95c2e4071</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>CONFIDO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Vertex AI, Kafka, Snowflake, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=e79e6e2ca3d5c032</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Technical Product Owner - Snowflake</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Acceldata</t>
+          <t>Forman Technology Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cost Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Zelis Healthcare</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,15 +2761,435 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=078e1151a7e26811</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>nProspect</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59d7a15394ef2be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Integration Engineer / ETL Developer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Concept Plus</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FHLBank San Francisco</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Java Backend Engineer/ Java Microservices Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71b106990543174f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Power BI Architect - Pharma domain- W2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Washington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, Cassandra, Splunk</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7-Eleven</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Santa Barbara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
         </is>

--- a/results/job_matches_2026-07-07.xlsx
+++ b/results/job_matches_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (Bilingual Mandarin Required)</t>
+          <t>Sr Data Engineer BI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Quality Bicycle Products GBC / QBP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83640374dcc1134d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcb545e0d7339df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (Bilingual Mandarin Required)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>HAVI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf10f975373c2da2</t>
+          <t>https://www.indeed.com/viewjob?jk=14e0af7fcb6718f5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quality Bicycle Products GBC / QBP</t>
+          <t>HAVI Logistics GmbH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcb545e0d7339df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7eb8898b893b80</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HAVI</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e0af7fcb6718f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5db19e3a9cbf828d</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7891b7fbaff3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3824264dc26ac6</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a787addd6be5560</t>
+          <t>https://www.indeed.com/viewjob?jk=2265ad8dcef15915</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - Data and Analytics</t>
+          <t>Senior Developer – Connected Customer (Loyalty Platform)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Google Cloud Platform, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53108c9bd68716fa</t>
+          <t>https://www.indeed.com/viewjob?jk=764638c30ee52f22</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2217093bc52c879</t>
+          <t>https://www.indeed.com/viewjob?jk=53108c9bd68716fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>DevOps Engineer II - Data and Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Azure, Google Cloud Platform, GCP, Hive</t>
+          <t>S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7744c06eb8bcb1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f2217093bc52c879</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Full Stack Developer - New York</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73a795e20ebb26</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5159354fa31a01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Azure, Google Cloud Platform, GCP, Hive</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f293050f94f852b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7744c06eb8bcb1d6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b685af16a4e1a32c</t>
+          <t>https://www.indeed.com/viewjob?jk=6409177a32a82f42</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401ff47825aadd13</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73a795e20ebb26</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb43d49de8a46b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f293050f94f852b1</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fb77a8047e2cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b685af16a4e1a32c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72319d23cc87f97d</t>
+          <t>https://www.indeed.com/viewjob?jk=401ff47825aadd13</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad85604b0a1225d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb43d49de8a46b2a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5d8aeb243630fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fb77a8047e2cb8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad39d3239661981</t>
+          <t>https://www.indeed.com/viewjob?jk=72319d23cc87f97d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cbd10dae618111f</t>
+          <t>https://www.indeed.com/viewjob?jk=bad85604b0a1225d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - New York</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5159354fa31a01</t>
+          <t>https://www.indeed.com/viewjob?jk=af5d8aeb243630fb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6409177a32a82f42</t>
+          <t>https://www.indeed.com/viewjob?jk=fad39d3239661981</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Research Application Support Engineer - Remote</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60c86e0a3c8c7263</t>
+          <t>https://www.indeed.com/viewjob?jk=6cbd10dae618111f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Research Application Support Engineer - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ede77cba151aef</t>
+          <t>https://www.indeed.com/viewjob?jk=60c86e0a3c8c7263</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Architect - Enterprise Systems</t>
+          <t>System Integration SME – Public Safety Systems Upgrade</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zagg</t>
+          <t>Cloud Destinations</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,69 +1676,69 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f88e375562aa037</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer, DevOps - Austin</t>
+          <t>Solution Architect - Enterprise Systems</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CS Disco</t>
+          <t>Zagg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, ECS, Scala, DynamoDB</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4fabdb31d720bc</t>
+          <t>https://www.indeed.com/viewjob?jk=db19210234d99ea0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sorenson Communications</t>
+          <t>Varsity Brands</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41305de4a58ac</t>
+          <t>https://www.indeed.com/viewjob?jk=668ddb7fa648f79b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Systems Analyst - Semantic Layer</t>
+          <t>Engineer, DevOps - Austin</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>CS Disco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, NoSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, ECS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3ffb67df20da06</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4fabdb31d720bc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GIS Software Engineer</t>
+          <t>Business Systems Analyst - Semantic Layer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, NoSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8c2320056095b2</t>
+          <t>https://www.indeed.com/viewjob?jk=97283fc0220405a0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Developer and Fintech</t>
+          <t>Business Systems Analyst - Semantic Layer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, NoSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94608c3ac7b4dac5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3ffb67df20da06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>AI Developer and Fintech</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e83a17dc9fa84d8</t>
+          <t>https://www.indeed.com/viewjob?jk=94608c3ac7b4dac5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Technologist - Institutional Operations Technology</t>
+          <t>GIS Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8c2320056095b2</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, Dask, Data Modeling, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbdbd7af12024ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer, LLM/AI Platforms</t>
+          <t>Data Engineer II - OIT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, Dask, Data Modeling, DataOps, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3629f388c5998ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II - OIT</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>BusPatrol</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09fc6de306f65311</t>
+          <t>https://www.indeed.com/viewjob?jk=68a96aefdc270e6c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BusPatrol</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a96aefdc270e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f578efcb4c089b6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef824e8a5755511</t>
+          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Virtusa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f578efcb4c089b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf6fb4571a3c426</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e79c2801587703</t>
+          <t>https://www.indeed.com/viewjob?jk=3c18066ab7c80217</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Data Engineer – Advanced Analytics &amp; Fraud Detection</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>TLN Worldwide Enterprises Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859a8b68a930992d</t>
+          <t>https://www.indeed.com/viewjob?jk=97e726717dc24fb3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d34fc4ec0585703</t>
+          <t>https://www.indeed.com/viewjob?jk=18521f120cecfb99</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>NFI Industries</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccc4b2641f8512d</t>
+          <t>https://www.indeed.com/viewjob?jk=850828fdab44abc4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Virtusa</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf6fb4571a3c426</t>
+          <t>https://www.indeed.com/viewjob?jk=d54c186e0fe4fd8f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer – Advanced Analytics &amp; Fraud Detection</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TLN Worldwide Enterprises Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97e726717dc24fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cbdf8c3d5d2aa6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18521f120cecfb99</t>
+          <t>https://www.indeed.com/viewjob?jk=859a8b68a930992d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850828fdab44abc4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d34fc4ec0585703</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer-Java, Spring Boot (Onsite)</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Athena, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7f4539113a6169</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccc4b2641f8512d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Sr. Software Engineer-Java, Spring Boot (Onsite)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cbdf8c3d5d2aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7f4539113a6169</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Technical Product Owner - Snowflake</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>Forman Technology Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cost Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Forman Technology Group</t>
+          <t>Zelis Healthcare</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b706dbf028db0cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=078e1151a7e26811</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cost Engineer</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Zelis Healthcare</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=078e1151a7e26811</t>
+          <t>https://www.indeed.com/viewjob?jk=59d7a15394ef2be5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Integration Engineer / ETL Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Concept Plus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling</t>
+          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d7a15394ef2be5</t>
+          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Integration Engineer / ETL Developer</t>
+          <t>Power BI Architect - Pharma domain- W2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Concept Plus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Informatica PowerCenter, Oracle, ETL, Talend, Power BI, Tableau, CI/CD, Bitbucket</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744245d6362a34a8</t>
+          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FHLBank San Francisco</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, MongoDB, Data Modeling, dbt, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+          <t>https://www.indeed.com/viewjob?jk=a602fd90cf822f8c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer/ Java Microservices Engineer</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, MongoDB, Data Modeling, dbt, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b106990543174f</t>
+          <t>https://www.indeed.com/viewjob?jk=095f422ac934ee58</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Power BI Architect - Pharma domain- W2</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, MongoDB, Data Modeling, dbt, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de37c16d0b1d6f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=deaff1cd6031383e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Acceldata</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, MongoDB, Data Modeling, dbt, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
+          <t>https://www.indeed.com/viewjob?jk=253a1410e2b36c94</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
+          <t>Senior Software Engineer, C&amp;I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, Cassandra, Splunk</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, MongoDB, Data Modeling, dbt, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=33fd0b602811c81f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Developer</t>
+          <t>Senior Java Backend Engineer/ Java Microservices Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
+          <t>https://www.indeed.com/viewjob?jk=71b106990543174f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sales Engineer - Hadoop Observability &amp; Open Data Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Acceldata</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, HDFS, Hive, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a16dbc986934bf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer III - Cloud Security - FCS Registration (Hybrid)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, Cassandra, Splunk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e288afbe233b4df</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer - Backend Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>API Gateway, Azure, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+          <t>https://www.indeed.com/viewjob?jk=badbffd0b2447e21</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,120 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3c5c90b1d831eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Santa Barbara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62e1461b847fc38f</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PEARLY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0fb523a054e4136</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=108facbefb6d2545</t>
         </is>
